--- a/DeviMaya_S388017/Timesheet Devi Maya.xlsx
+++ b/DeviMaya_S388017/Timesheet Devi Maya.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devi/Documents/GitHub/PRT585-SOFTWARE-ENGINEERING-PRACTICE/DeviMaya_S388017/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E971303-6967-C44D-B05F-FBB149CC50C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3142B6D-A640-A949-BBFD-FF40AF0926AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Individual timesheet" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="Role work timesheet" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Individual timesheet'!$A$2:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Role work timesheet'!$A$2:$E$2</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="46">
   <si>
     <t>EACH INDIVIDUAL MUST HAVE TO ENTER 6 HOURS TIME LOGGING IN THIS PAGE PER EACH WEEK</t>
   </si>
@@ -121,6 +122,69 @@
   <si>
     <t>Project work: start drafting ERD
 Current diagram is using PlantUML, will try to move to better visualisation option later</t>
+  </si>
+  <si>
+    <t>Week-5</t>
+  </si>
+  <si>
+    <t>Hours [1-4]</t>
+  </si>
+  <si>
+    <t>(DA): SQL fundamentals study</t>
+  </si>
+  <si>
+    <t>(DA): Research of non-RDB database types: Redis</t>
+  </si>
+  <si>
+    <t>(BA): Research of 'basic' SRS deliverables</t>
+  </si>
+  <si>
+    <t>(BA): Research how is gantt chart/WBS used in project management</t>
+  </si>
+  <si>
+    <t>(BA): Research on using PlantUML instead of visual paradigm/draw io</t>
+  </si>
+  <si>
+    <t>(BA): Research on using mermaid gantt instead of a more visual option</t>
+  </si>
+  <si>
+    <t>(DA): Research on elasticsearch</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>(DA): Self study of wide column &amp; graph database</t>
+  </si>
+  <si>
+    <t>(DA): Self study of scaling, sharding, normalisation vs denormalisation</t>
+  </si>
+  <si>
+    <t>(DA): Self study: data modelling</t>
+  </si>
+  <si>
+    <t>(DA): NoSQL refresher</t>
+  </si>
+  <si>
+    <t>(BA): Refresh FR/NFR/Acceptance criteria fundamentals</t>
+  </si>
+  <si>
+    <t>Project work: Review Figma</t>
+  </si>
+  <si>
+    <t>Project work: update SRS with new acceptance criterias</t>
+  </si>
+  <si>
+    <t>Individiual study: Jobtrackr</t>
+  </si>
+  <si>
+    <t>Individual study: SecureVault</t>
+  </si>
+  <si>
+    <t>Individual study: SecureVault (finish 1E)</t>
   </si>
 </sst>
 </file>
@@ -662,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F177"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.83203125" style="4" customWidth="1"/>
@@ -907,11 +971,113 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E19" s="19"/>
-    </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E36"/>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="E16" s="25"/>
+    </row>
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="4">
+        <v>2</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="37" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E37"/>
@@ -926,7 +1092,7 @@
       <c r="E40"/>
     </row>
     <row r="41" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E41" s="24"/>
+      <c r="E41"/>
     </row>
     <row r="42" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E42" s="24"/>
@@ -943,23 +1109,21 @@
     <row r="46" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E46" s="24"/>
     </row>
-    <row r="48" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E48" s="9"/>
+    <row r="47" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E47" s="24"/>
     </row>
     <row r="49" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D49" s="10"/>
       <c r="E49" s="9"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E66" s="4"/>
-    </row>
-    <row r="68" spans="1:5" ht="77.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="11"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
-    </row>
+    <row r="50" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D50" s="10"/>
+      <c r="E50" s="9"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E67" s="4"/>
+    </row>
+    <row r="69" spans="1:5" ht="77.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="11"/>
       <c r="B75" s="11"/>
@@ -982,49 +1146,47 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="11"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" s="18"/>
+      <c r="A80" s="11"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="18"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="18"/>
-      <c r="E82" s="12"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="18"/>
+      <c r="E83" s="12"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="18"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B85"/>
+      <c r="A85" s="18"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B86"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B87"/>
-      <c r="E87"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B88"/>
+      <c r="E88"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B89"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B90"/>
-      <c r="E90"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" s="13"/>
-      <c r="B93" s="13"/>
-      <c r="C93" s="13"/>
-      <c r="D93" s="13"/>
-      <c r="E93" s="14"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B91"/>
+      <c r="E91"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="13"/>
@@ -1040,14 +1202,14 @@
       <c r="D95" s="13"/>
       <c r="E95" s="14"/>
     </row>
-    <row r="96" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="13"/>
       <c r="B96" s="13"/>
       <c r="C96" s="13"/>
       <c r="D96" s="13"/>
       <c r="E96" s="14"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="13"/>
       <c r="B97" s="13"/>
       <c r="C97" s="13"/>
@@ -1061,9 +1223,12 @@
       <c r="D98" s="13"/>
       <c r="E98" s="14"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A101" s="13"/>
-      <c r="E101"/>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="13"/>
+      <c r="B99" s="13"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="14"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="13"/>
@@ -1085,30 +1250,30 @@
       <c r="A106" s="13"/>
       <c r="E106"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A108" s="13"/>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="13"/>
+      <c r="E107"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="13"/>
-      <c r="B109"/>
-      <c r="E109" s="4"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="13"/>
+      <c r="B110"/>
+      <c r="E110" s="4"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="13"/>
-      <c r="E111"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="13"/>
+      <c r="E112"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="13"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A115" s="13"/>
-      <c r="D115" s="15"/>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" s="13"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="13"/>
@@ -1118,11 +1283,11 @@
       <c r="A117" s="13"/>
       <c r="D117" s="15"/>
     </row>
-    <row r="118" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="13"/>
       <c r="D118" s="15"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="13"/>
       <c r="D119" s="15"/>
     </row>
@@ -1131,17 +1296,18 @@
       <c r="D120" s="15"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" s="13"/>
       <c r="D121" s="15"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122" s="13"/>
+      <c r="D122" s="15"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="13"/>
-      <c r="E123"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="13"/>
+      <c r="E124"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="13"/>
@@ -1152,12 +1318,8 @@
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="13"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A129" s="13"/>
-      <c r="B129" s="16"/>
-      <c r="C129" s="16"/>
-      <c r="D129" s="23"/>
-      <c r="E129" s="17"/>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" s="13"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="13"/>
@@ -1171,14 +1333,14 @@
       <c r="B131" s="16"/>
       <c r="C131" s="16"/>
       <c r="D131" s="23"/>
-      <c r="E131" s="16"/>
+      <c r="E131" s="17"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="13"/>
       <c r="B132" s="16"/>
       <c r="C132" s="16"/>
       <c r="D132" s="23"/>
-      <c r="E132" s="17"/>
+      <c r="E132" s="16"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="13"/>
@@ -1194,8 +1356,12 @@
       <c r="D134" s="23"/>
       <c r="E134" s="17"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A136" s="13"/>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135" s="13"/>
+      <c r="B135" s="16"/>
+      <c r="C135" s="16"/>
+      <c r="D135" s="23"/>
+      <c r="E135" s="17"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="13"/>
@@ -1212,10 +1378,8 @@
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="13"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A143" s="13"/>
-      <c r="B143" s="16"/>
-      <c r="E143" s="21"/>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142" s="13"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="13"/>
@@ -1230,22 +1394,22 @@
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="13"/>
       <c r="B146" s="16"/>
-      <c r="E146" s="22"/>
+      <c r="E146" s="21"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="13"/>
       <c r="B147" s="16"/>
-      <c r="E147" s="21"/>
+      <c r="E147" s="22"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="13"/>
       <c r="B148" s="16"/>
       <c r="E148" s="21"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A150" s="13"/>
-      <c r="B150" s="20"/>
-      <c r="E150" s="17"/>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A149" s="13"/>
+      <c r="B149" s="16"/>
+      <c r="E149" s="21"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="13"/>
@@ -1255,12 +1419,12 @@
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="13"/>
       <c r="B152" s="20"/>
-      <c r="E152" s="16"/>
+      <c r="E152" s="17"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="13"/>
       <c r="B153" s="20"/>
-      <c r="E153" s="17"/>
+      <c r="E153" s="16"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="13"/>
@@ -1269,10 +1433,12 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="13"/>
+      <c r="B155" s="20"/>
       <c r="E155" s="17"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A157" s="13"/>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A156" s="13"/>
+      <c r="E156" s="17"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="13"/>
@@ -1324,7 +1490,6 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" s="13"/>
-      <c r="B174" s="20"/>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" s="13"/>
@@ -1332,9 +1497,13 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" s="13"/>
+      <c r="B176" s="20"/>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A177" s="20"/>
+      <c r="A177" s="13"/>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A178" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -1343,15 +1512,725 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0542F39-F0FF-42BC-8522-46D8537566B3}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDECAF1A-CFDE-8A4D-8627-1C98D56A0BCE}">
+  <dimension ref="A1:F178"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="36.5" style="4" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="122" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1640625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="18"/>
+      <c r="B7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="E12"/>
+    </row>
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17"/>
+      <c r="C17"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B18"/>
+      <c r="C18"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B19"/>
+      <c r="C19"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="E20" s="19"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B21"/>
+      <c r="C21"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B22"/>
+      <c r="C22"/>
+    </row>
+    <row r="37" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E37"/>
+    </row>
+    <row r="38" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E38"/>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E39"/>
+    </row>
+    <row r="40" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E40"/>
+    </row>
+    <row r="41" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E41"/>
+    </row>
+    <row r="42" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E42" s="24"/>
+    </row>
+    <row r="43" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E43" s="24"/>
+    </row>
+    <row r="44" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E44" s="24"/>
+    </row>
+    <row r="45" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E45" s="24"/>
+    </row>
+    <row r="46" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E46" s="24"/>
+    </row>
+    <row r="47" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E47" s="24"/>
+    </row>
+    <row r="49" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="E49" s="9"/>
+    </row>
+    <row r="50" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D50" s="10"/>
+      <c r="E50" s="9"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E67" s="4"/>
+    </row>
+    <row r="69" spans="1:5" ht="77.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="11"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="11"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="11"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="11"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="11"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="11"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="18"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="18"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" s="18"/>
+      <c r="E83" s="12"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="18"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="18"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B86"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B87"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B88"/>
+      <c r="E88"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B89"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B90"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B91"/>
+      <c r="E91"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" s="13"/>
+      <c r="B94" s="13"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="14"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" s="13"/>
+      <c r="B95" s="13"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="13"/>
+      <c r="E95" s="14"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" s="13"/>
+      <c r="B96" s="13"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="13"/>
+      <c r="E96" s="14"/>
+    </row>
+    <row r="97" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="13"/>
+      <c r="B97" s="13"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="13"/>
+      <c r="E97" s="14"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="13"/>
+      <c r="B98" s="13"/>
+      <c r="C98" s="13"/>
+      <c r="D98" s="13"/>
+      <c r="E98" s="14"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="13"/>
+      <c r="B99" s="13"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="14"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="13"/>
+      <c r="E102"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="13"/>
+      <c r="E103"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="13"/>
+      <c r="E104"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" s="13"/>
+      <c r="E105"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="13"/>
+      <c r="E106"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="13"/>
+      <c r="E107"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" s="13"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="13"/>
+      <c r="B110"/>
+      <c r="E110" s="4"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" s="13"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="13"/>
+      <c r="E112"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" s="13"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" s="13"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" s="13"/>
+      <c r="D116" s="15"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" s="13"/>
+      <c r="D117" s="15"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" s="13"/>
+      <c r="D118" s="15"/>
+    </row>
+    <row r="119" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="13"/>
+      <c r="D119" s="15"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" s="13"/>
+      <c r="D120" s="15"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" s="13"/>
+      <c r="D121" s="15"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D122" s="15"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" s="13"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" s="13"/>
+      <c r="E124"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="13"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" s="13"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" s="13"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" s="13"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130" s="13"/>
+      <c r="B130" s="16"/>
+      <c r="C130" s="16"/>
+      <c r="D130" s="23"/>
+      <c r="E130" s="17"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131" s="13"/>
+      <c r="B131" s="16"/>
+      <c r="C131" s="16"/>
+      <c r="D131" s="23"/>
+      <c r="E131" s="17"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132" s="13"/>
+      <c r="B132" s="16"/>
+      <c r="C132" s="16"/>
+      <c r="D132" s="23"/>
+      <c r="E132" s="16"/>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133" s="13"/>
+      <c r="B133" s="16"/>
+      <c r="C133" s="16"/>
+      <c r="D133" s="23"/>
+      <c r="E133" s="17"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A134" s="13"/>
+      <c r="B134" s="16"/>
+      <c r="C134" s="16"/>
+      <c r="D134" s="23"/>
+      <c r="E134" s="17"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135" s="13"/>
+      <c r="B135" s="16"/>
+      <c r="C135" s="16"/>
+      <c r="D135" s="23"/>
+      <c r="E135" s="17"/>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A137" s="13"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138" s="13"/>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139" s="13"/>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140" s="13"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141" s="13"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142" s="13"/>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A144" s="13"/>
+      <c r="B144" s="16"/>
+      <c r="E144" s="21"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A145" s="13"/>
+      <c r="B145" s="16"/>
+      <c r="E145" s="21"/>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A146" s="13"/>
+      <c r="B146" s="16"/>
+      <c r="E146" s="21"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A147" s="13"/>
+      <c r="B147" s="16"/>
+      <c r="E147" s="22"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A148" s="13"/>
+      <c r="B148" s="16"/>
+      <c r="E148" s="21"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A149" s="13"/>
+      <c r="B149" s="16"/>
+      <c r="E149" s="21"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A151" s="13"/>
+      <c r="B151" s="20"/>
+      <c r="E151" s="17"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A152" s="13"/>
+      <c r="B152" s="20"/>
+      <c r="E152" s="17"/>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153" s="13"/>
+      <c r="B153" s="20"/>
+      <c r="E153" s="16"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A154" s="13"/>
+      <c r="B154" s="20"/>
+      <c r="E154" s="17"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A155" s="13"/>
+      <c r="B155" s="20"/>
+      <c r="E155" s="17"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A156" s="13"/>
+      <c r="E156" s="17"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A158" s="13"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A159" s="13"/>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A160" s="13"/>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" s="13"/>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" s="13"/>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" s="13"/>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" s="13"/>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" s="13"/>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" s="13"/>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" s="13"/>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" s="13"/>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" s="13"/>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170" s="13"/>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171" s="13"/>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172" s="13"/>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173" s="13"/>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174" s="13"/>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175" s="13"/>
+      <c r="B175" s="20"/>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176" s="13"/>
+      <c r="B176" s="20"/>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A177" s="13"/>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A178" s="20"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008A37478F0D103C418E1983367D0E3B29" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0e52e73692c282c4b11ce339126e795d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a01afa4-83d8-4578-8116-1fe20cdd06b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d364ad524074f3044f8606d9c9b001a2" ns2:_="">
     <xsd:import namespace="1a01afa4-83d8-4578-8116-1fe20cdd06b6"/>
@@ -1489,22 +2368,21 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5DBCEA-0785-438C-AB6D-531696C8FF28}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC89AADA-5F80-4891-A851-84363269EAD3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1522,19 +2400,11 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E2D867-194E-458C-A857-FF5EE3277888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5DBCEA-0785-438C-AB6D-531696C8FF28}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/DeviMaya_S388017/Timesheet Devi Maya.xlsx
+++ b/DeviMaya_S388017/Timesheet Devi Maya.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devi/Documents/GitHub/PRT585-SOFTWARE-ENGINEERING-PRACTICE/DeviMaya_S388017/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3142B6D-A640-A949-BBFD-FF40AF0926AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D952FD-538C-5148-B010-923029E661B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Individual timesheet" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="53">
   <si>
     <t>EACH INDIVIDUAL MUST HAVE TO ENTER 6 HOURS TIME LOGGING IN THIS PAGE PER EACH WEEK</t>
   </si>
@@ -185,13 +185,34 @@
   </si>
   <si>
     <t>Individual study: SecureVault (finish 1E)</t>
+  </si>
+  <si>
+    <t>Prepare BA &amp; DA study pathway document</t>
+  </si>
+  <si>
+    <t>Finish activity diagram</t>
+  </si>
+  <si>
+    <t>Week-6</t>
+  </si>
+  <si>
+    <t>BA: self-study system design, dropbox case study</t>
+  </si>
+  <si>
+    <t>BA: self-study system design, dropbox case study (finish domain-related FR and NFR)</t>
+  </si>
+  <si>
+    <t>DA: self-study system design, dropbox case study</t>
+  </si>
+  <si>
+    <t>DA: self-study system design, dropbox case study (finish conceptual entity list, capacity estimation practice)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -265,14 +286,6 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -396,20 +409,20 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -950,7 +963,7 @@
       <c r="D14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="24" t="s">
         <v>23</v>
       </c>
     </row>
@@ -967,7 +980,7 @@
       <c r="D15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="24" t="s">
         <v>24</v>
       </c>
     </row>
@@ -975,7 +988,7 @@
       <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
-      <c r="E16" s="25"/>
+      <c r="E16" s="24"/>
     </row>
     <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
@@ -1079,6 +1092,108 @@
         <v>45</v>
       </c>
     </row>
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="4">
+        <v>2</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="37" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E37"/>
     </row>
@@ -1095,22 +1210,22 @@
       <c r="E41"/>
     </row>
     <row r="42" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E42" s="24"/>
+      <c r="E42" s="23"/>
     </row>
     <row r="43" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E43" s="24"/>
+      <c r="E43" s="23"/>
     </row>
     <row r="44" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E44" s="24"/>
+      <c r="E44" s="23"/>
     </row>
     <row r="45" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E45" s="24"/>
+      <c r="E45" s="23"/>
     </row>
     <row r="46" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E46" s="24"/>
+      <c r="E46" s="23"/>
     </row>
     <row r="47" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E47" s="24"/>
+      <c r="E47" s="23"/>
     </row>
     <row r="49" spans="4:5" x14ac:dyDescent="0.2">
       <c r="E49" s="9"/>
@@ -1325,42 +1440,42 @@
       <c r="A130" s="13"/>
       <c r="B130" s="16"/>
       <c r="C130" s="16"/>
-      <c r="D130" s="23"/>
+      <c r="D130" s="22"/>
       <c r="E130" s="17"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="13"/>
       <c r="B131" s="16"/>
       <c r="C131" s="16"/>
-      <c r="D131" s="23"/>
+      <c r="D131" s="22"/>
       <c r="E131" s="17"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="13"/>
       <c r="B132" s="16"/>
       <c r="C132" s="16"/>
-      <c r="D132" s="23"/>
+      <c r="D132" s="22"/>
       <c r="E132" s="16"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="13"/>
       <c r="B133" s="16"/>
       <c r="C133" s="16"/>
-      <c r="D133" s="23"/>
+      <c r="D133" s="22"/>
       <c r="E133" s="17"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="13"/>
       <c r="B134" s="16"/>
       <c r="C134" s="16"/>
-      <c r="D134" s="23"/>
+      <c r="D134" s="22"/>
       <c r="E134" s="17"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="13"/>
       <c r="B135" s="16"/>
       <c r="C135" s="16"/>
-      <c r="D135" s="23"/>
+      <c r="D135" s="22"/>
       <c r="E135" s="17"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
@@ -1384,56 +1499,56 @@
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="13"/>
       <c r="B144" s="16"/>
-      <c r="E144" s="21"/>
+      <c r="E144" s="20"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="13"/>
       <c r="B145" s="16"/>
-      <c r="E145" s="21"/>
+      <c r="E145" s="20"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="13"/>
       <c r="B146" s="16"/>
-      <c r="E146" s="21"/>
+      <c r="E146" s="20"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="13"/>
       <c r="B147" s="16"/>
-      <c r="E147" s="22"/>
+      <c r="E147" s="21"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="13"/>
       <c r="B148" s="16"/>
-      <c r="E148" s="21"/>
+      <c r="E148" s="20"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="13"/>
       <c r="B149" s="16"/>
-      <c r="E149" s="21"/>
+      <c r="E149" s="20"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="13"/>
-      <c r="B151" s="20"/>
+      <c r="B151" s="19"/>
       <c r="E151" s="17"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="13"/>
-      <c r="B152" s="20"/>
+      <c r="B152" s="19"/>
       <c r="E152" s="17"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="13"/>
-      <c r="B153" s="20"/>
+      <c r="B153" s="19"/>
       <c r="E153" s="16"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="13"/>
-      <c r="B154" s="20"/>
+      <c r="B154" s="19"/>
       <c r="E154" s="17"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="13"/>
-      <c r="B155" s="20"/>
+      <c r="B155" s="19"/>
       <c r="E155" s="17"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
@@ -1493,17 +1608,17 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" s="13"/>
-      <c r="B175" s="20"/>
+      <c r="B175" s="19"/>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" s="13"/>
-      <c r="B176" s="20"/>
+      <c r="B176" s="19"/>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A177" s="13"/>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A178" s="20"/>
+      <c r="A178" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -1744,7 +1859,7 @@
       <c r="D15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="24" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1765,28 +1880,79 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B17"/>
       <c r="C17"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B18"/>
-      <c r="C18"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B19"/>
-      <c r="C19"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="E20" s="19"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B21"/>
-      <c r="C21"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B22"/>
       <c r="C22"/>
     </row>
@@ -1806,22 +1972,22 @@
       <c r="E41"/>
     </row>
     <row r="42" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E42" s="24"/>
+      <c r="E42" s="23"/>
     </row>
     <row r="43" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E43" s="24"/>
+      <c r="E43" s="23"/>
     </row>
     <row r="44" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E44" s="24"/>
+      <c r="E44" s="23"/>
     </row>
     <row r="45" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E45" s="24"/>
+      <c r="E45" s="23"/>
     </row>
     <row r="46" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E46" s="24"/>
+      <c r="E46" s="23"/>
     </row>
     <row r="47" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E47" s="24"/>
+      <c r="E47" s="23"/>
     </row>
     <row r="49" spans="4:5" x14ac:dyDescent="0.2">
       <c r="E49" s="9"/>
@@ -2036,42 +2202,42 @@
       <c r="A130" s="13"/>
       <c r="B130" s="16"/>
       <c r="C130" s="16"/>
-      <c r="D130" s="23"/>
+      <c r="D130" s="22"/>
       <c r="E130" s="17"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="13"/>
       <c r="B131" s="16"/>
       <c r="C131" s="16"/>
-      <c r="D131" s="23"/>
+      <c r="D131" s="22"/>
       <c r="E131" s="17"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="13"/>
       <c r="B132" s="16"/>
       <c r="C132" s="16"/>
-      <c r="D132" s="23"/>
+      <c r="D132" s="22"/>
       <c r="E132" s="16"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="13"/>
       <c r="B133" s="16"/>
       <c r="C133" s="16"/>
-      <c r="D133" s="23"/>
+      <c r="D133" s="22"/>
       <c r="E133" s="17"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="13"/>
       <c r="B134" s="16"/>
       <c r="C134" s="16"/>
-      <c r="D134" s="23"/>
+      <c r="D134" s="22"/>
       <c r="E134" s="17"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="13"/>
       <c r="B135" s="16"/>
       <c r="C135" s="16"/>
-      <c r="D135" s="23"/>
+      <c r="D135" s="22"/>
       <c r="E135" s="17"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
@@ -2095,56 +2261,56 @@
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="13"/>
       <c r="B144" s="16"/>
-      <c r="E144" s="21"/>
+      <c r="E144" s="20"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="13"/>
       <c r="B145" s="16"/>
-      <c r="E145" s="21"/>
+      <c r="E145" s="20"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="13"/>
       <c r="B146" s="16"/>
-      <c r="E146" s="21"/>
+      <c r="E146" s="20"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="13"/>
       <c r="B147" s="16"/>
-      <c r="E147" s="22"/>
+      <c r="E147" s="21"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="13"/>
       <c r="B148" s="16"/>
-      <c r="E148" s="21"/>
+      <c r="E148" s="20"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="13"/>
       <c r="B149" s="16"/>
-      <c r="E149" s="21"/>
+      <c r="E149" s="20"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="13"/>
-      <c r="B151" s="20"/>
+      <c r="B151" s="19"/>
       <c r="E151" s="17"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="13"/>
-      <c r="B152" s="20"/>
+      <c r="B152" s="19"/>
       <c r="E152" s="17"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="13"/>
-      <c r="B153" s="20"/>
+      <c r="B153" s="19"/>
       <c r="E153" s="16"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="13"/>
-      <c r="B154" s="20"/>
+      <c r="B154" s="19"/>
       <c r="E154" s="17"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="13"/>
-      <c r="B155" s="20"/>
+      <c r="B155" s="19"/>
       <c r="E155" s="17"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
@@ -2204,17 +2370,17 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" s="13"/>
-      <c r="B175" s="20"/>
+      <c r="B175" s="19"/>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" s="13"/>
-      <c r="B176" s="20"/>
+      <c r="B176" s="19"/>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A177" s="13"/>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A178" s="20"/>
+      <c r="A178" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
